--- a/clients/大晃産業/03_日程調整/【段取り】研修準備スケジュール.xlsx
+++ b/clients/大晃産業/03_日程調整/【段取り】研修準備スケジュール.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>研修の目的・選抜理由・心構えを記載</t>
+          <t>打合せ時に検討</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>役割・期待・関わり方を記載</t>
+          <t>打合せ時に検討</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>第11回（4月予定）1泊2日</t>
+          <t>打合せ時に検討</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,11 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>打合せ時に検討</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
@@ -1048,7 +1052,11 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>打合せ時に検討</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="n">
